--- a/E/FLOOR.xlsx
+++ b/E/FLOOR.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
   <si>
     <t/>
   </si>
@@ -38,6 +38,36 @@
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>20142501</t>
+  </si>
+  <si>
+    <t>INDOFOD SNACK ASSORT</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20142532</t>
+  </si>
+  <si>
+    <t>STT PARTY PACK 6'S</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20142552</t>
+  </si>
+  <si>
+    <t>GARUDA PARTY PACK</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
 </sst>
 </file>
@@ -430,14 +460,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -497,6 +527,66 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/FLOOR.xlsx
+++ b/E/FLOOR.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="19">
   <si>
     <t/>
   </si>
@@ -460,17 +460,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -489,8 +490,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -506,11 +513,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -526,11 +533,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -546,11 +553,11 @@
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -566,11 +573,11 @@
       <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -586,7 +593,7 @@
       <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/FLOOR.xlsx
+++ b/E/FLOOR.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
   <si>
     <t/>
   </si>
@@ -460,18 +460,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -490,14 +489,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -513,11 +506,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -533,11 +526,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -553,11 +546,11 @@
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -573,11 +566,11 @@
       <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -593,7 +586,7 @@
       <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/FLOOR.xlsx
+++ b/E/FLOOR.xlsx
@@ -19,7 +19,7 @@
     <t>20104133</t>
   </si>
   <si>
-    <t>DK SNACK ASORTED 12S</t>
+    <t>DK SNACK ASORTED</t>
   </si>
   <si>
     <t>FLOOR</t>
